--- a/data/trans_orig/P32D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32D_R-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año en 2023</t>
+          <t>Población que se dio un atracón de alcohol más de una vez al mes en el último año en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11929</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29065</t>
+          <t>29328</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2394</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>14216</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37191</t>
+          <t>36928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253210</t>
+          <t>252947</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270710</t>
+          <t>270346</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>147867</t>
+          <t>147183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>159005</t>
+          <t>158978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>406482</t>
+          <t>406745</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>426842</t>
+          <t>427154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>7730</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>21745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6552</t>
+          <t>6457</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20312</t>
+          <t>19162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16913</t>
+          <t>16687</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35382</t>
+          <t>34878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>189700</t>
+          <t>190427</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204321</t>
+          <t>204442</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>113590</t>
+          <t>114740</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>127350</t>
+          <t>127445</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>310692</t>
+          <t>311196</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329161</t>
+          <t>329387</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19064</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41393</t>
+          <t>42180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>596</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22155</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44792</t>
+          <t>44878</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168986</t>
+          <t>168199</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>191315</t>
+          <t>190639</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34234</t>
+          <t>34352</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39002</t>
+          <t>39118</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>205301</t>
+          <t>205215</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>227938</t>
+          <t>227889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27179</t>
+          <t>27974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51978</t>
+          <t>52535</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,82 +1774,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>5,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,3%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>10615</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2408</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24691</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,56%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>5,95%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>49284</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>24461</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>70475</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>5,33%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,19%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10615</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2232</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>24533</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>49284</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>21966</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>69095</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,62%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>457961</t>
+          <t>457404</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>482760</t>
+          <t>481965</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,82 +1887,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>94,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>404151</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>390075</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>412358</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>97,44%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>94,05%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,42%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>762</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>875421</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>854230</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>900244</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>94,67%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>404151</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>390233</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>412534</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>875421</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>855610</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>902739</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>94,67%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,35%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22112</t>
+          <t>22724</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46923</t>
+          <t>49551</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4517</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14118</t>
+          <t>14332</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28337</t>
+          <t>30084</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56536</t>
+          <t>56202</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>180245</t>
+          <t>177617</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>205056</t>
+          <t>204444</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115251</t>
+          <t>115037</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>124852</t>
+          <t>125137</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300000</t>
+          <t>300334</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>328199</t>
+          <t>326452</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,56%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17688</t>
+          <t>19210</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>5546</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21778</t>
+          <t>21438</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10720</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32823</t>
+          <t>30756</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76097</t>
+          <t>74575</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91861</t>
+          <t>91774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>99575</t>
+          <t>99915</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115248</t>
+          <t>115807</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>182315</t>
+          <t>184382</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>204418</t>
+          <t>205284</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,42%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>118037</t>
+          <t>116736</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164526</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>27618</t>
+          <t>24647</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70326</t>
+          <t>71148</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>146203</t>
+          <t>149150</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>226718</t>
+          <t>227462</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,97%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1371191</t>
+          <t>1368572</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1417680</t>
+          <t>1418981</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>930176</t>
+          <t>929354</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>972884</t>
+          <t>975855</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2309501</t>
+          <t>2308757</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2390016</t>
+          <t>2387069</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32D_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P32D_R-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19201</t>
+          <t>20435</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11929</t>
+          <t>12282</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29328</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>2614</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>25428</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16519</t>
+          <t>18032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36928</t>
+          <t>40073</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>263074</t>
+          <t>282498</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>252947</t>
+          <t>271944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>270346</t>
+          <t>290651</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>155171</t>
+          <t>167522</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>147183</t>
+          <t>160416</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>158978</t>
+          <t>171386</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>418245</t>
+          <t>450021</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>406745</t>
+          <t>436860</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>427154</t>
+          <t>458901</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>282275</t>
+          <t>302933</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>282275</t>
+          <t>302933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>282275</t>
+          <t>302933</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>161399</t>
+          <t>174000</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>161399</t>
+          <t>174000</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>161399</t>
+          <t>174000</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>443673</t>
+          <t>476933</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>443673</t>
+          <t>476933</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>443673</t>
+          <t>476933</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13641</t>
+          <t>15329</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7730</t>
+          <t>8582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21745</t>
+          <t>24185</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11625</t>
+          <t>13377</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>7444</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19162</t>
+          <t>22249</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>25267</t>
+          <t>28706</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>19713</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34878</t>
+          <t>40233</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>198531</t>
+          <t>208452</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>190427</t>
+          <t>199596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>204442</t>
+          <t>215199</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>122277</t>
+          <t>132290</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114740</t>
+          <t>123418</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>127445</t>
+          <t>138223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>320807</t>
+          <t>340742</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>311196</t>
+          <t>329215</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>329387</t>
+          <t>349735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>94,66%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>212172</t>
+          <t>223781</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>212172</t>
+          <t>223781</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>212172</t>
+          <t>223781</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133902</t>
+          <t>145667</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133902</t>
+          <t>145667</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133902</t>
+          <t>145667</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>346074</t>
+          <t>369448</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>346074</t>
+          <t>369448</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>346074</t>
+          <t>369448</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>31967</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>21531</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42180</t>
+          <t>45178</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>7886</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>31484</t>
+          <t>35514</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>24254</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>44878</t>
+          <t>49417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,1%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>181093</t>
+          <t>195102</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>168199</t>
+          <t>181891</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>190639</t>
+          <t>205538</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37516</t>
+          <t>42343</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34352</t>
+          <t>38004</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39118</t>
+          <t>44551</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>218609</t>
+          <t>237445</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>205215</t>
+          <t>223542</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>227889</t>
+          <t>248705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,11%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>210379</t>
+          <t>227069</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>210379</t>
+          <t>227069</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>210379</t>
+          <t>227069</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>45890</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>45890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>39714</t>
+          <t>45890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>250093</t>
+          <t>272959</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>250093</t>
+          <t>272959</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>250093</t>
+          <t>272959</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38669</t>
+          <t>41813</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27974</t>
+          <t>30502</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52535</t>
+          <t>55126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>14840</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24691</t>
+          <t>22885</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>49284</t>
+          <t>56653</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24461</t>
+          <t>44429</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>70475</t>
+          <t>73431</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>471270</t>
+          <t>502259</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>457404</t>
+          <t>488946</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>481965</t>
+          <t>513570</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>404151</t>
+          <t>215599</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>390075</t>
+          <t>207554</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>412358</t>
+          <t>221559</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>875421</t>
+          <t>717859</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>854230</t>
+          <t>701081</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>900244</t>
+          <t>730083</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>509939</t>
+          <t>544072</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>509939</t>
+          <t>544072</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>509939</t>
+          <t>544072</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>414766</t>
+          <t>230439</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>414766</t>
+          <t>230439</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>414766</t>
+          <t>230439</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>924705</t>
+          <t>774512</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>924705</t>
+          <t>774512</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>924705</t>
+          <t>774512</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>33076</t>
+          <t>42071</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22724</t>
+          <t>29579</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49551</t>
+          <t>58724</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>4607</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41165</t>
+          <t>50519</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30084</t>
+          <t>37749</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56202</t>
+          <t>69448</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>194092</t>
+          <t>211061</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>177617</t>
+          <t>194408</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>204444</t>
+          <t>223553</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>121280</t>
+          <t>143009</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>115037</t>
+          <t>137482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125137</t>
+          <t>146850</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>315371</t>
+          <t>354070</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>300334</t>
+          <t>335141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>326452</t>
+          <t>366840</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>227168</t>
+          <t>253132</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>227168</t>
+          <t>253132</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>227168</t>
+          <t>253132</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>356536</t>
+          <t>404589</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>356536</t>
+          <t>404589</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>356536</t>
+          <t>404589</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>17908</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>12072</t>
+          <t>13550</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5546</t>
+          <t>6495</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21438</t>
+          <t>24793</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18709</t>
+          <t>19634</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>10587</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30756</t>
+          <t>32745</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>87148</t>
+          <t>78659</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74575</t>
+          <t>66835</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91774</t>
+          <t>83070</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>109281</t>
+          <t>112927</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>99915</t>
+          <t>101684</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115807</t>
+          <t>119982</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>196429</t>
+          <t>191586</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>184382</t>
+          <t>178475</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>205284</t>
+          <t>200633</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,42%</t>
+          <t>94,99%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>93785</t>
+          <t>84743</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>93785</t>
+          <t>84743</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>93785</t>
+          <t>84743</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>121353</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>121353</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>121353</t>
+          <t>126477</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>215138</t>
+          <t>211220</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>215138</t>
+          <t>211220</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>215138</t>
+          <t>211220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>140510</t>
+          <t>157699</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>116736</t>
+          <t>133444</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>167145</t>
+          <t>187123</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>50827</t>
+          <t>60240</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24647</t>
+          <t>48015</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71148</t>
+          <t>79187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>191337</t>
+          <t>217939</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>149150</t>
+          <t>186832</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>227462</t>
+          <t>249417</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1395207</t>
+          <t>1478032</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1368572</t>
+          <t>1448608</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1418981</t>
+          <t>1502287</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>949675</t>
+          <t>813691</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>929354</t>
+          <t>794744</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>975855</t>
+          <t>825916</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2344882</t>
+          <t>2291723</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2308757</t>
+          <t>2260245</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2387069</t>
+          <t>2322830</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>92,56%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1535717</t>
+          <t>1635731</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1535717</t>
+          <t>1635731</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1535717</t>
+          <t>1635731</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1000502</t>
+          <t>873931</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1000502</t>
+          <t>873931</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1000502</t>
+          <t>873931</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2536219</t>
+          <t>2509662</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>2536219</t>
+          <t>2509662</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>2536219</t>
+          <t>2509662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
